--- a/output/roomself_excel/7086.xlsx
+++ b/output/roomself_excel/7086.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109193</v>
+        <v>98115</v>
       </c>
       <c r="D2" t="n">
-        <v>3816</v>
+        <v>2608</v>
       </c>
       <c r="E2" t="n">
-        <v>859</v>
+        <v>386</v>
       </c>
       <c r="F2" t="n">
-        <v>152</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>133034</v>
+        <v>180729</v>
       </c>
       <c r="D3" t="n">
-        <v>3216</v>
+        <v>3416</v>
       </c>
       <c r="E3" t="n">
-        <v>859</v>
+        <v>745</v>
       </c>
       <c r="F3" t="n">
-        <v>457</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43218</v>
+        <v>113373</v>
       </c>
       <c r="D4" t="n">
-        <v>2448</v>
+        <v>2696</v>
       </c>
       <c r="E4" t="n">
-        <v>535</v>
+        <v>432</v>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7367</v>
+        <v>45840</v>
       </c>
       <c r="D5" t="n">
-        <v>768</v>
+        <v>1892</v>
       </c>
       <c r="E5" t="n">
-        <v>158</v>
+        <v>434</v>
       </c>
       <c r="F5" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2809</v>
+        <v>30719</v>
       </c>
       <c r="D6" t="n">
-        <v>424</v>
+        <v>1440</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,17 +576,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2756</v>
+        <v>39043</v>
       </c>
       <c r="D7" t="n">
-        <v>420</v>
+        <v>1776</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>221</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2756</v>
+        <v>76323</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>2224</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>344</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>98115</v>
+        <v>109193</v>
       </c>
       <c r="D9" t="n">
-        <v>2608</v>
+        <v>3816</v>
       </c>
       <c r="E9" t="n">
-        <v>745</v>
+        <v>859</v>
       </c>
       <c r="F9" t="n">
-        <v>193</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>76323</v>
+        <v>133034</v>
       </c>
       <c r="D10" t="n">
-        <v>2224</v>
+        <v>3216</v>
       </c>
       <c r="E10" t="n">
-        <v>344</v>
+        <v>457</v>
       </c>
       <c r="F10" t="n">
-        <v>276</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>56396</v>
+        <v>43218</v>
       </c>
       <c r="D11" t="n">
-        <v>1992</v>
+        <v>2448</v>
       </c>
       <c r="E11" t="n">
-        <v>745</v>
+        <v>535</v>
       </c>
       <c r="F11" t="n">
-        <v>293</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22672</v>
+        <v>7367</v>
       </c>
       <c r="D12" t="n">
-        <v>1288</v>
+        <v>768</v>
       </c>
       <c r="E12" t="n">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>113373</v>
+        <v>2809</v>
       </c>
       <c r="D13" t="n">
-        <v>2696</v>
+        <v>424</v>
       </c>
       <c r="E13" t="n">
-        <v>745</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>432</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4995</v>
+        <v>2756</v>
       </c>
       <c r="D14" t="n">
-        <v>624</v>
+        <v>420</v>
       </c>
       <c r="E14" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>45840</v>
+        <v>2756</v>
       </c>
       <c r="D15" t="n">
-        <v>1892</v>
+        <v>420</v>
       </c>
       <c r="E15" t="n">
-        <v>851</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>258</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74160</v>
+        <v>56396</v>
       </c>
       <c r="D16" t="n">
-        <v>2196</v>
+        <v>1992</v>
       </c>
       <c r="E16" t="n">
-        <v>745</v>
+        <v>382</v>
       </c>
       <c r="F16" t="n">
-        <v>240</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3304</v>
+        <v>22672</v>
       </c>
       <c r="D17" t="n">
-        <v>460</v>
+        <v>1288</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10115</v>
+        <v>4995</v>
       </c>
       <c r="D18" t="n">
-        <v>816</v>
+        <v>624</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30719</v>
+        <v>74160</v>
       </c>
       <c r="D19" t="n">
-        <v>1440</v>
+        <v>2196</v>
       </c>
       <c r="E19" t="n">
-        <v>314</v>
+        <v>240</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>19240</v>
+        <v>3304</v>
       </c>
       <c r="D20" t="n">
-        <v>1148</v>
+        <v>460</v>
       </c>
       <c r="E20" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39043</v>
+        <v>10115</v>
       </c>
       <c r="D21" t="n">
-        <v>1776</v>
+        <v>816</v>
       </c>
       <c r="E21" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3422</v>
+        <v>19240</v>
       </c>
       <c r="D22" t="n">
-        <v>468</v>
+        <v>1148</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>132208</v>
+        <v>3422</v>
       </c>
       <c r="D23" t="n">
-        <v>3140</v>
+        <v>468</v>
       </c>
       <c r="E23" t="n">
-        <v>589</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>131400</v>
+        <v>132208</v>
       </c>
       <c r="D24" t="n">
-        <v>3264</v>
+        <v>3140</v>
       </c>
       <c r="E24" t="n">
-        <v>851</v>
+        <v>589</v>
       </c>
       <c r="F24" t="n">
-        <v>487</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>69553</v>
+        <v>131400</v>
       </c>
       <c r="D25" t="n">
-        <v>3516</v>
+        <v>3264</v>
       </c>
       <c r="E25" t="n">
-        <v>400</v>
+        <v>487</v>
       </c>
       <c r="F25" t="n">
-        <v>241</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>180729</v>
+        <v>69553</v>
       </c>
       <c r="D26" t="n">
-        <v>3416</v>
+        <v>3516</v>
       </c>
       <c r="E26" t="n">
-        <v>1077</v>
+        <v>400</v>
       </c>
       <c r="F26" t="n">
-        <v>745</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27">

--- a/output/roomself_excel/7086.xlsx
+++ b/output/roomself_excel/7086.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2608</v>
       </c>
-      <c r="E2" t="n">
-        <v>386</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>193</v>
+        <v>367</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>165</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3416</v>
       </c>
-      <c r="E3" t="n">
-        <v>745</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>628</v>
+        <v>387</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>448</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>2696</v>
       </c>
-      <c r="E4" t="n">
-        <v>432</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>290</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>1892</v>
       </c>
-      <c r="E5" t="n">
-        <v>434</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>156</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,12 @@
       <c r="D6" t="n">
         <v>1440</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>1776</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>221</v>
       </c>
-      <c r="F7" t="n">
-        <v>19</v>
-      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +683,27 @@
       <c r="D8" t="n">
         <v>2224</v>
       </c>
-      <c r="E8" t="n">
-        <v>344</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>276</v>
+        <v>309</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>247</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -629,11 +721,27 @@
       <c r="D9" t="n">
         <v>3816</v>
       </c>
-      <c r="E9" t="n">
-        <v>859</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>152</v>
+        <v>266</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>821</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +759,20 @@
       <c r="D10" t="n">
         <v>3216</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>457</v>
       </c>
-      <c r="F10" t="n">
-        <v>19</v>
-      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>2448</v>
       </c>
-      <c r="E11" t="n">
-        <v>535</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>115</v>
+        <v>96</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>516</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +827,27 @@
       <c r="D12" t="n">
         <v>768</v>
       </c>
-      <c r="E12" t="n">
-        <v>158</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>139</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J12" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +865,20 @@
       <c r="D13" t="n">
         <v>424</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>53</v>
       </c>
-      <c r="F13" t="n">
-        <v>19</v>
-      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +895,20 @@
       <c r="D14" t="n">
         <v>420</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>52</v>
       </c>
-      <c r="F14" t="n">
-        <v>19</v>
-      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +925,20 @@
       <c r="D15" t="n">
         <v>420</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>52</v>
       </c>
-      <c r="F15" t="n">
-        <v>19</v>
-      </c>
+      <c r="G15" t="n">
+        <v>19</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +955,20 @@
       <c r="D16" t="n">
         <v>1992</v>
       </c>
-      <c r="E16" t="n">
-        <v>382</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>264</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +985,27 @@
       <c r="D17" t="n">
         <v>1288</v>
       </c>
-      <c r="E17" t="n">
-        <v>247</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
+        <v>104</v>
+      </c>
+      <c r="G17" t="n">
+        <v>29</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>218</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +1023,20 @@
       <c r="D18" t="n">
         <v>624</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>111</v>
       </c>
-      <c r="F18" t="n">
-        <v>19</v>
-      </c>
+      <c r="G18" t="n">
+        <v>19</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1053,20 @@
       <c r="D19" t="n">
         <v>2196</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>240</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>35</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1083,12 @@
       <c r="D20" t="n">
         <v>460</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1105,12 @@
       <c r="D21" t="n">
         <v>816</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1127,12 @@
       <c r="D22" t="n">
         <v>1148</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1149,12 @@
       <c r="D23" t="n">
         <v>468</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1171,20 @@
       <c r="D24" t="n">
         <v>3140</v>
       </c>
-      <c r="E24" t="n">
-        <v>589</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>324</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1201,27 @@
       <c r="D25" t="n">
         <v>3264</v>
       </c>
-      <c r="E25" t="n">
-        <v>487</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>299</v>
+        <v>263</v>
+      </c>
+      <c r="G25" t="n">
+        <v>35</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>452</v>
+      </c>
+      <c r="J25" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="26">
@@ -1003,11 +1239,27 @@
       <c r="D26" t="n">
         <v>3516</v>
       </c>
-      <c r="E26" t="n">
-        <v>400</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>364</v>
+      </c>
+      <c r="G26" t="n">
+        <v>35</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>206</v>
+      </c>
+      <c r="J26" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -1025,11 +1277,27 @@
       <c r="D27" t="n">
         <v>2780</v>
       </c>
-      <c r="E27" t="n">
-        <v>307</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>244</v>
+        <v>288</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>225</v>
+      </c>
+      <c r="J27" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -1047,11 +1315,27 @@
       <c r="D28" t="n">
         <v>2708</v>
       </c>
-      <c r="E28" t="n">
-        <v>296</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>242</v>
+        <v>277</v>
+      </c>
+      <c r="G28" t="n">
+        <v>19</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>206</v>
+      </c>
+      <c r="J28" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
